--- a/src/instructions/module_1/spatial_frequency_staircase/[ES]spatial_frequency_staircase_instructions.xlsx
+++ b/src/instructions/module_1/spatial_frequency_staircase/[ES]spatial_frequency_staircase_instructions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akoun\Desktop\Biocruces\begibraintool\src\instructions\module_1\spatial_frequency_staircase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A65A771-0826-4DC0-827C-7BC8DC434902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BA1965-CCF0-4100-8FDF-547AB22324DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="4605" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8205" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>title</t>
   </si>
@@ -143,25 +143,7 @@
     <t>1.png</t>
   </si>
   <si>
-    <t>2.png</t>
-  </si>
-  <si>
-    <t>3.png</t>
-  </si>
-  <si>
     <t>4.png</t>
-  </si>
-  <si>
-    <t>Observa las líneas que aparecen en la pantalla.
-Indica en qué dirección apuntan.</t>
-  </si>
-  <si>
-    <t>Si las líneas van de izquierda a derecha,
-pulsa el botón derecho.</t>
-  </si>
-  <si>
-    <t>Si las líneas van de derecha a izquierda,
-pulsa el botón izquierdo.</t>
   </si>
   <si>
     <t>Si no lo ves con claridad
@@ -174,6 +156,22 @@
   </si>
   <si>
     <t>instructions\module_1\spatial_frequency_staircase\</t>
+  </si>
+  <si>
+    <t>2&amp;3.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durante esta prueba debes observar las líneas que aparecen en el centro de la pantalla.
+</t>
+  </si>
+  <si>
+    <t>Cuando las veas, tendras que indicar en qué dirección apuntan.
+Si las líneas van de izquierda a derecha,
+tendrás que pulsar el botón derecho.</t>
+  </si>
+  <si>
+    <t>Si las líneas van de derecha a izquierda,
+pulsarás el botón izquierdo.</t>
   </si>
 </sst>
 </file>
@@ -638,34 +636,34 @@
         <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
         <v>18</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
       </c>
       <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
         <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
       </c>
       <c r="L2" t="s">
         <v>13</v>
@@ -685,18 +683,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -814,14 +812,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -832,6 +822,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
